--- a/Automation.xlsx
+++ b/Automation.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seacen-my.sharepoint.com/personal/ahmad_aizudeen_seacen_org/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seacen-my.sharepoint.com/personal/ahmad_aizudeen_seacen_org/Documents/Desktop/NLP Project/cfm-nlp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57D68E0E-6BDF-408D-B983-7034BF414120}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2098365A-20DD-45BE-ADC3-3971340C760A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
+    <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
   </bookViews>
   <sheets>
     <sheet name="BoP" sheetId="1" r:id="rId1"/>
     <sheet name="Taiwan BoP" sheetId="4" r:id="rId2"/>
     <sheet name="BoP edit" sheetId="3" r:id="rId3"/>
-    <sheet name="IIP" sheetId="2" r:id="rId4"/>
+    <sheet name="IIP edit" sheetId="2" r:id="rId4"/>
+    <sheet name="Taiwan IIP" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="BoxPlot">"BoxPlot"</definedName>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="189">
   <si>
     <t>Malaysia</t>
   </si>
@@ -265,9 +266,6 @@
     <t>IIP: Assets: Official Reserve Assets</t>
   </si>
   <si>
-    <t>Taiwan</t>
-  </si>
-  <si>
     <t>IIP: Assets: Direct Investment: Equity and Investment Fund Shares</t>
   </si>
   <si>
@@ -506,6 +504,129 @@
   </si>
   <si>
     <t>desc2</t>
+  </si>
+  <si>
+    <t>IIP: Assets: Direct Investment</t>
+  </si>
+  <si>
+    <t>IIP: Assets: Portfolio Investment</t>
+  </si>
+  <si>
+    <t>IIP: Assets: Other Investment</t>
+  </si>
+  <si>
+    <t>International Investment Assets</t>
+  </si>
+  <si>
+    <t>IIP: Assets</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Direct Investment</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Direct Investment: Equity</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Direct Investment: Debt Instruments</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Portfolio Investment</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Portfolio Investment: Equity</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Portfolio Investment: Debt Securities</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Financial Derivatives &amp; Employee Stock Options</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Other Equity</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Currency &amp; Deposits</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Loans</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Insurance, Pension &amp; Standardized Guarantee Schemes</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Trade Credit &amp; Advances</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Other Accounts Receivable</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: SDRs</t>
+  </si>
+  <si>
+    <t>Official Reserve Liabilities</t>
+  </si>
+  <si>
+    <t>International Investment Liabilities</t>
+  </si>
+  <si>
+    <t>International Investment Position (IIP): Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IIP: Assets: Direct Investment </t>
+  </si>
+  <si>
+    <t>IIP: Assets: Portfolio Investment (PI)</t>
+  </si>
+  <si>
+    <t>IIP: Assets: Other Investment (OI)</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities (Liab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IIP: Liab: Direct Investment </t>
+  </si>
+  <si>
+    <t>IIP: Liab: Direct Investment: Equity and Investment Fund Shares</t>
+  </si>
+  <si>
+    <t>IIP: Liab: Direct Investment: Debt Instruments</t>
+  </si>
+  <si>
+    <t>IIP: Liab: Portfolio Investment (PI)</t>
+  </si>
+  <si>
+    <t>IIP: Liab: PI: Equity and Investment Fund Shares (ES)</t>
+  </si>
+  <si>
+    <t>IIP: Liab: PI: Debt Securities (DS)</t>
+  </si>
+  <si>
+    <t>IIP: Liab: Financial Derivatives (FD)</t>
+  </si>
+  <si>
+    <t>IIP: Liab: Other Investment (OI)</t>
+  </si>
+  <si>
+    <t>IIP: Liab: OI: Other Equity</t>
+  </si>
+  <si>
+    <t>IIP: Liab: OI: DI: Currency and Deposits (CD)</t>
+  </si>
+  <si>
+    <t>IIP: Liab: OI: DI: Loans</t>
+  </si>
+  <si>
+    <t>IIP: Liab: OI: DI: Trade Credits and Advances</t>
+  </si>
+  <si>
+    <t>IIP: Liab: OI: DI: Other Accounts Payable (OP)</t>
   </si>
 </sst>
 </file>
@@ -609,7 +730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -621,11 +742,32 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -759,10 +901,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1083,14 +1221,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D07C09-2566-4E87-AFBD-4FC06A7EBECB}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="90.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="90.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C1">
         <v>2023</v>
       </c>
@@ -1101,7 +1239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1118,7 +1256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1129,7 +1267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1140,7 +1278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1151,7 +1289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1162,7 +1300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1173,7 +1311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1195,7 +1333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1206,7 +1344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1217,7 +1355,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1228,7 +1366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1242,7 +1380,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
         <v>4</v>
       </c>
@@ -1253,7 +1391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
@@ -1264,7 +1402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1275,7 +1413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1286,7 +1424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1297,7 +1435,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -1308,7 +1446,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1322,22 +1460,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1348,7 +1486,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
         <v>13</v>
       </c>
@@ -1356,93 +1494,93 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G26" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G28" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G29" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G30" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G31" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G32" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G33" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G34" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G35" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G36" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G37" s="1" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B25">
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="8" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G3 G5:G7 G9:G15 G17:G20">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1453,31 +1591,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E63BC1-BED3-4747-8D06-F85558E49DF4}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1485,13 +1623,13 @@
         <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -1499,13 +1637,13 @@
         <v>15</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1513,13 +1651,13 @@
         <v>16</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1527,13 +1665,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1541,13 +1679,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1555,13 +1693,13 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -1569,13 +1707,13 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1583,13 +1721,13 @@
         <v>21</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1597,13 +1735,13 @@
         <v>22</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1611,13 +1749,13 @@
         <v>23</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1625,13 +1763,13 @@
         <v>24</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1639,13 +1777,13 @@
         <v>26</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1653,13 +1791,13 @@
         <v>27</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
@@ -1667,209 +1805,209 @@
         <v>28</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="C19" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="C23" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="B24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C25" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="3" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" s="9" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="9" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
@@ -1877,13 +2015,13 @@
         <v>40</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
@@ -1891,13 +2029,13 @@
         <v>33</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
@@ -1905,13 +2043,13 @@
         <v>34</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>40</v>
       </c>
@@ -1919,13 +2057,13 @@
         <v>36</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
@@ -1933,7 +2071,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>39</v>
@@ -1941,17 +2079,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D3:D15">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D17:D28">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:D34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1962,25 +2100,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8963A901-D89C-4B28-A001-1133E7499D08}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="94.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1991,7 +2129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2002,7 +2140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2013,7 +2151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2021,10 +2159,10 @@
         <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2035,7 +2173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2046,7 +2184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -2057,7 +2195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2065,10 +2203,10 @@
         <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -2079,7 +2217,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -2090,7 +2228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -2101,7 +2239,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2112,7 +2250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -2123,7 +2261,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2134,7 +2272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -2145,7 +2283,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
@@ -2153,10 +2291,10 @@
         <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>40</v>
       </c>
@@ -2167,7 +2305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
@@ -2178,7 +2316,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -2189,7 +2327,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
@@ -2200,179 +2338,179 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="C25" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B27" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="C29" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="3" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="3" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" s="1" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C16 C18:C21">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23:C35">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2383,225 +2521,830 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6A0191-4B64-4498-9156-E0F972E58559}">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.140625" customWidth="1"/>
-    <col min="2" max="2" width="76.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" customWidth="1"/>
+    <col min="3" max="3" width="76.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C33">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A40F74-391E-4B15-A339-8F1D52070F5D}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" customWidth="1"/>
+    <col min="3" max="3" width="56.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C15" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>78</v>
-      </c>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D31" s="1"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D31">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{cf3212bd-797d-4ecd-a8a7-8deb8b8877aa}" enabled="1" method="Standard" siteId="{703b977e-4eb6-4dfc-af2d-db5f73a01b26}" contentBits="0" removed="0"/>
+  <clbl:label id="{cf3212bd-797d-4ecd-a8a7-8deb8b8877aa}" enabled="1" method="Standard" siteId="{703b977e-4eb6-4dfc-af2d-db5f73a01b26}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/Automation.xlsx
+++ b/Automation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seacen-my.sharepoint.com/personal/ahmad_aizudeen_seacen_org/Documents/Desktop/NLP Project/cfm-nlp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41ebccb2aabfff33/Desktop/data science project/cfm-nlp/cfm-nlp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="397" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2098365A-20DD-45BE-ADC3-3971340C760A}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE95FB0F-6447-48AE-985A-AC896BD13437}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
   </bookViews>
   <sheets>
     <sheet name="BoP" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="188">
   <si>
     <t>Malaysia</t>
   </si>
@@ -567,9 +567,6 @@
   </si>
   <si>
     <t>IIP: Liabilities: Other Investment: SDRs</t>
-  </si>
-  <si>
-    <t>Official Reserve Liabilities</t>
   </si>
   <si>
     <t>International Investment Liabilities</t>
@@ -1221,14 +1218,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D07C09-2566-4E87-AFBD-4FC06A7EBECB}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="68.54296875" customWidth="1"/>
-    <col min="6" max="6" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="90.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="90.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1">
         <v>2023</v>
       </c>
@@ -1239,7 +1236,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1256,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1267,7 +1264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1278,7 +1275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1289,7 +1286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1300,7 +1297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1311,7 +1308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1322,7 +1319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1333,7 +1330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,7 +1341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1355,7 +1352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1366,7 +1363,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1380,7 +1377,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>4</v>
       </c>
@@ -1391,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
@@ -1402,7 +1399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1413,7 +1410,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1424,7 +1421,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1435,7 +1432,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -1446,7 +1443,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1460,22 +1457,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1486,7 +1483,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>13</v>
       </c>
@@ -1494,62 +1491,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G26" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G28" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G29" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G30" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G31" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G32" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G33" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G34" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G35" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G36" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G37" s="1" t="s">
         <v>55</v>
       </c>
@@ -1591,17 +1588,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E63BC1-BED3-4747-8D06-F85558E49DF4}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="77.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.26953125" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -1615,7 +1612,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1629,7 +1626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -1643,7 +1640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1657,7 +1654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1671,7 +1668,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1685,7 +1682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1699,7 +1696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -1713,7 +1710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1727,7 +1724,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1741,7 +1738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1755,7 +1752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1769,7 +1766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1783,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1797,7 +1794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
@@ -1811,7 +1808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>83</v>
       </c>
@@ -1825,7 +1822,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>83</v>
       </c>
@@ -1839,7 +1836,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -1853,7 +1850,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>84</v>
       </c>
@@ -1867,7 +1864,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>84</v>
       </c>
@@ -1881,7 +1878,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -1895,7 +1892,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>90</v>
       </c>
@@ -1909,7 +1906,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>85</v>
       </c>
@@ -1923,7 +1920,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>85</v>
       </c>
@@ -1937,7 +1934,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -1951,7 +1948,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -1965,7 +1962,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>85</v>
       </c>
@@ -1979,7 +1976,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>85</v>
       </c>
@@ -1993,7 +1990,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -2007,7 +2004,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
@@ -2021,7 +2018,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
@@ -2035,7 +2032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
@@ -2049,7 +2046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>40</v>
       </c>
@@ -2063,7 +2060,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
@@ -2100,14 +2097,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8963A901-D89C-4B28-A001-1133E7499D08}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="94.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -2118,7 +2115,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -2129,7 +2126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2140,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2151,7 +2148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2162,7 +2159,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2173,7 +2170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2184,7 +2181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -2195,7 +2192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2206,7 +2203,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -2217,7 +2214,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -2228,7 +2225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -2239,7 +2236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2250,7 +2247,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -2261,7 +2258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2272,7 +2269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -2283,7 +2280,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
@@ -2294,7 +2291,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>40</v>
       </c>
@@ -2305,7 +2302,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
@@ -2316,7 +2313,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -2327,7 +2324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
@@ -2338,7 +2335,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>83</v>
       </c>
@@ -2349,7 +2346,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>83</v>
       </c>
@@ -2360,7 +2357,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>83</v>
       </c>
@@ -2371,7 +2368,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>84</v>
       </c>
@@ -2382,7 +2379,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
@@ -2393,7 +2390,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>84</v>
       </c>
@@ -2404,7 +2401,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>90</v>
       </c>
@@ -2415,7 +2412,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -2426,7 +2423,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -2437,7 +2434,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
@@ -2448,7 +2445,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>85</v>
       </c>
@@ -2459,7 +2456,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>85</v>
       </c>
@@ -2470,7 +2467,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -2481,7 +2478,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>85</v>
       </c>
@@ -2492,7 +2489,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>85</v>
       </c>
@@ -2522,14 +2519,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6A0191-4B64-4498-9156-E0F972E58559}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" customWidth="1"/>
-    <col min="3" max="3" width="76.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="76.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -2540,7 +2537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -2551,7 +2548,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2562,7 +2559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2573,7 +2570,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2584,7 +2581,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2595,7 +2592,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2606,7 +2603,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -2617,7 +2614,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2628,7 +2625,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -2639,7 +2636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -2650,7 +2647,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -2661,7 +2658,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2672,7 +2669,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -2683,7 +2680,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2694,7 +2691,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -2705,7 +2702,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>151</v>
       </c>
@@ -2716,7 +2713,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -2727,7 +2724,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>83</v>
       </c>
@@ -2738,7 +2735,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>83</v>
       </c>
@@ -2749,7 +2746,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -2760,7 +2757,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
@@ -2771,7 +2768,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -2782,7 +2779,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>90</v>
       </c>
@@ -2793,7 +2790,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -2804,7 +2801,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -2815,7 +2812,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>85</v>
       </c>
@@ -2826,7 +2823,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>85</v>
       </c>
@@ -2837,7 +2834,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -2848,7 +2845,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -2859,7 +2856,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
@@ -2870,23 +2867,23 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
-        <v>169</v>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>167</v>
@@ -2903,16 +2900,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A40F74-391E-4B15-A339-8F1D52070F5D}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" customWidth="1"/>
-    <col min="3" max="3" width="56.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="76.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="3" max="3" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -2926,7 +2923,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>151</v>
       </c>
@@ -2934,13 +2931,13 @@
         <v>151</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2948,13 +2945,13 @@
         <v>14</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2968,7 +2965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -2982,7 +2979,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2990,13 +2987,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -3010,7 +3007,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -3024,7 +3021,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -3038,7 +3035,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -3046,13 +3043,13 @@
         <v>21</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -3066,7 +3063,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -3080,7 +3077,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -3094,7 +3091,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -3108,7 +3105,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -3122,7 +3119,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -3136,21 +3133,21 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -3158,13 +3155,13 @@
         <v>83</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>83</v>
       </c>
@@ -3172,13 +3169,13 @@
         <v>86</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>83</v>
       </c>
@@ -3186,13 +3183,13 @@
         <v>87</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -3200,13 +3197,13 @@
         <v>84</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
@@ -3214,13 +3211,13 @@
         <v>88</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -3228,13 +3225,13 @@
         <v>89</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>90</v>
       </c>
@@ -3242,13 +3239,13 @@
         <v>90</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -3256,13 +3253,13 @@
         <v>85</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -3270,13 +3267,13 @@
         <v>91</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>85</v>
       </c>
@@ -3284,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>85</v>
       </c>
@@ -3298,13 +3295,13 @@
         <v>93</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -3312,13 +3309,13 @@
         <v>95</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -3326,13 +3323,13 @@
         <v>96</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D31" s="1"/>
     </row>
   </sheetData>

--- a/Automation.xlsx
+++ b/Automation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41ebccb2aabfff33/Desktop/data science project/cfm-nlp/cfm-nlp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seacen-my.sharepoint.com/personal/ahmad_aizudeen_seacen_org/Documents/Desktop/NLP Project/cfm-nlp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE95FB0F-6447-48AE-985A-AC896BD13437}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C610087B-7FCC-42B4-A34A-6449F75CE754}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
   </bookViews>
   <sheets>
     <sheet name="BoP" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="189">
   <si>
     <t>Malaysia</t>
   </si>
@@ -624,6 +624,9 @@
   </si>
   <si>
     <t>IIP: Liab: OI: DI: Other Accounts Payable (OP)</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Other Accounts Payable</t>
   </si>
 </sst>
 </file>
@@ -2864,7 +2867,7 @@
         <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">

--- a/Automation.xlsx
+++ b/Automation.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="400" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE95FB0F-6447-48AE-985A-AC896BD13437}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
   </bookViews>
   <sheets>
     <sheet name="BoP" sheetId="1" r:id="rId1"/>
@@ -898,6 +898,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Automation.xlsx
+++ b/Automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41ebccb2aabfff33/Desktop/data science project/cfm-nlp/cfm-nlp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE95FB0F-6447-48AE-985A-AC896BD13437}"/>
+  <xr:revisionPtr revIDLastSave="404" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{210A789F-99F6-49CF-8312-56B73C95F10E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
   </bookViews>
   <sheets>
     <sheet name="BoP" sheetId="1" r:id="rId1"/>
@@ -560,9 +560,6 @@
     <t>IIP: Liabilities: Other Investment: Trade Credit &amp; Advances</t>
   </si>
   <si>
-    <t>IIP: Liabilities: Other Investment: Other Accounts Receivable</t>
-  </si>
-  <si>
     <t>IIP: Liabilities</t>
   </si>
   <si>
@@ -624,6 +621,9 @@
   </si>
   <si>
     <t>IIP: Liab: OI: DI: Other Accounts Payable (OP)</t>
+  </si>
+  <si>
+    <t>IIP: Liabilities: Other Investment: Other Accounts Payable</t>
   </si>
 </sst>
 </file>
@@ -898,10 +898,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2103,7 +2099,7 @@
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="94.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2868,7 +2864,7 @@
         <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2879,18 +2875,18 @@
         <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2935,7 +2931,7 @@
         <v>151</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>152</v>
@@ -2949,7 +2945,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>148</v>
@@ -2991,7 +2987,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>149</v>
@@ -3047,7 +3043,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>150</v>
@@ -3139,16 +3135,16 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3159,7 +3155,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>153</v>
@@ -3173,7 +3169,7 @@
         <v>86</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>154</v>
@@ -3187,7 +3183,7 @@
         <v>87</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>155</v>
@@ -3201,7 +3197,7 @@
         <v>84</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>156</v>
@@ -3215,7 +3211,7 @@
         <v>88</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>157</v>
@@ -3229,7 +3225,7 @@
         <v>89</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>158</v>
@@ -3243,7 +3239,7 @@
         <v>90</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>159</v>
@@ -3257,7 +3253,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>160</v>
@@ -3271,7 +3267,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>161</v>
@@ -3285,7 +3281,7 @@
         <v>92</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>162</v>
@@ -3299,7 +3295,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>163</v>
@@ -3313,7 +3309,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>165</v>
@@ -3327,10 +3323,10 @@
         <v>96</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">

--- a/Automation.xlsx
+++ b/Automation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41ebccb2aabfff33/Desktop/data science project/cfm-nlp/cfm-nlp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seacen-my.sharepoint.com/personal/ahmad_aizudeen_seacen_org/Documents/Desktop/NLP Project/cfm-nlp/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="404" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{210A789F-99F6-49CF-8312-56B73C95F10E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
   </bookViews>
   <sheets>
     <sheet name="BoP" sheetId="1" r:id="rId1"/>
@@ -1218,14 +1218,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D07C09-2566-4E87-AFBD-4FC06A7EBECB}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="90.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="90.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C1">
         <v>2023</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
         <v>4</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1457,22 +1457,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
         <v>13</v>
       </c>
@@ -1491,62 +1491,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G26" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G28" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G29" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G30" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G31" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G32" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G33" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G34" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G35" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G36" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G37" s="1" t="s">
         <v>55</v>
       </c>
@@ -1588,17 +1588,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E63BC1-BED3-4747-8D06-F85558E49DF4}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>83</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>83</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>84</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>84</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>90</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>85</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>85</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>85</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>85</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>40</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
@@ -2097,14 +2097,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8963A901-D89C-4B28-A001-1133E7499D08}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="94.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>40</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>83</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>83</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>83</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>84</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>84</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>90</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>85</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>85</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>85</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>85</v>
       </c>
@@ -2519,14 +2519,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6A0191-4B64-4498-9156-E0F972E58559}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
-    <col min="3" max="3" width="76.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" customWidth="1"/>
+    <col min="3" max="3" width="76.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>151</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>83</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>83</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>90</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>85</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>85</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>85</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>168</v>
       </c>
@@ -2900,16 +2900,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A40F74-391E-4B15-A339-8F1D52070F5D}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
-    <col min="3" max="3" width="56.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="76.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" customWidth="1"/>
+    <col min="3" max="3" width="56.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>151</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>168</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>83</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>83</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>90</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>85</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>85</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D31" s="1"/>
     </row>
   </sheetData>

--- a/Automation.xlsx
+++ b/Automation.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="404" documentId="8_{BD8F74E7-7E59-459D-A077-317051AEA3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{210A789F-99F6-49CF-8312-56B73C95F10E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{413002D4-9AA9-4179-9D7E-643D619B9574}"/>
   </bookViews>
   <sheets>
     <sheet name="BoP" sheetId="1" r:id="rId1"/>
